--- a/tools/myCustomBlockly/iMi/ChargeEsp32/ChargeEsp32積木程式碼.xlsx
+++ b/tools/myCustomBlockly/iMi/ChargeEsp32/ChargeEsp32積木程式碼.xlsx
@@ -972,30 +972,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">      current_mA = ina219Car.getCurrent_mA(;//Current</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFED7D31"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t>負載電流</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFED7D31"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>(mA)</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">      power_mW = ina219Car.getPower_mW();//Power</t>
     </r>
     <r>
@@ -1566,6 +1542,31 @@
       </rPr>
       <t>'</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">      current_mA = ina219Car.getCurrent_mA();//Current</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFED7D31"/>
+        <rFont val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>負載電流</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFED7D31"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(mA)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3018,7 +3019,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B2" s="18" t="str">
         <f>IF(NOT(ISBLANK(A2)),A2&amp;"\n","")</f>
@@ -3035,7 +3036,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B3" s="18" t="str">
         <f t="shared" ref="B3:B66" si="0">IF(NOT(ISBLANK(A3)),A3&amp;"\n","")</f>
@@ -3056,7 +3057,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B4" s="18" t="str">
         <f t="shared" si="0"/>
@@ -3067,7 +3068,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B5" s="18" t="str">
         <f t="shared" si="0"/>
@@ -3081,7 +3082,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B6" s="18" t="str">
         <f t="shared" si="0"/>
@@ -3092,7 +3093,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B7" s="18" t="str">
         <f t="shared" si="0"/>
@@ -3106,7 +3107,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B8" s="18" t="str">
         <f t="shared" si="0"/>
@@ -3117,7 +3118,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B9" s="18" t="str">
         <f t="shared" si="0"/>
@@ -3131,7 +3132,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B10" s="18" t="str">
         <f t="shared" si="0"/>
@@ -3156,7 +3157,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" s="18" t="str">
         <f t="shared" si="0"/>
@@ -3167,7 +3168,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B13" s="18" t="str">
         <f t="shared" si="0"/>
@@ -3178,7 +3179,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B14" s="18" t="str">
         <f t="shared" si="0"/>
@@ -3989,9 +3990,9 @@
       <c r="J1" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="6" t="e">
-        <f ca="1">"var code ="&amp;_xlfn.CONCAT(J2:J4)&amp;";"</f>
-        <v>#NAME?</v>
+      <c r="K1" s="6" t="str">
+        <f>"var code ="&amp;J2&amp;J3&amp;J4&amp;";"</f>
+        <v>var code = '//WiFi'+'\n'+ 'const char* ssid = '+value_ssid+';'+'\n'+ 'const char* password = '+value_wifipwd+';'+'\n'+;</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="28.2" x14ac:dyDescent="0.3">
@@ -4008,7 +4009,7 @@
       </c>
       <c r="H2" s="25"/>
       <c r="I2" s="28" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J2" s="18" t="str">
         <f>IF(ISBLANK(I2),"",I2&amp;"+'\n'+")</f>
@@ -4033,7 +4034,7 @@
       </c>
       <c r="H3" s="26"/>
       <c r="I3" s="28" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J3" s="18" t="str">
         <f t="shared" ref="J3:J66" si="2">IF(ISBLANK(I3),"",I3&amp;"+'\n'+")</f>
@@ -4055,7 +4056,7 @@
       </c>
       <c r="H4" s="25"/>
       <c r="I4" s="28" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J4" s="18" t="str">
         <f t="shared" si="2"/>
@@ -5582,9 +5583,9 @@
       <c r="J1" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="6" t="e">
-        <f ca="1">"var code ="&amp;_xlfn.CONCAT(J2:J4)&amp;";"</f>
-        <v>#NAME?</v>
+      <c r="K1" s="6" t="str">
+        <f>"var code ="&amp;J2&amp;J3&amp;J4&amp;J5&amp;";"</f>
+        <v>var code = '//google 試算表'+'\n'+ 'String sheetId='+value_sheetid+';//試算表id'+'\n'+ 'String sheetTag="";'+'\n'+ 'const char* sTag = '+value_stag+';//工作表名稱'+'\n'+;</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="28.2" x14ac:dyDescent="0.3">
@@ -5601,7 +5602,7 @@
       </c>
       <c r="H2" s="25"/>
       <c r="I2" s="28" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J2" s="18" t="str">
         <f>IF(ISBLANK(I2),"",I2&amp;"+'\n'+")</f>
@@ -5626,7 +5627,7 @@
       </c>
       <c r="H3" s="26"/>
       <c r="I3" s="28" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J3" s="18" t="str">
         <f t="shared" ref="J3:J66" si="2">IF(ISBLANK(I3),"",I3&amp;"+'\n'+")</f>
@@ -5648,7 +5649,7 @@
       </c>
       <c r="H4" s="25"/>
       <c r="I4" s="28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J4" s="18" t="str">
         <f t="shared" si="2"/>
@@ -5670,7 +5671,7 @@
       </c>
       <c r="H5" s="26"/>
       <c r="I5" s="28" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J5" s="18" t="str">
         <f t="shared" si="2"/>
@@ -22940,7 +22941,7 @@
   <dimension ref="A1:E999"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.88671875" customWidth="1"/>
+    <col min="1" max="1" width="43.109375" customWidth="1"/>
     <col min="2" max="2" width="23.77734375" customWidth="1"/>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
   </cols>
@@ -22954,7 +22955,7 @@
       </c>
       <c r="D1" s="7" t="str">
         <f>"Blockly.Arduino.functions_['"&amp;D2&amp;"'] = '"&amp;D3&amp;"';"</f>
-        <v>Blockly.Arduino.functions_['_01imi_espcharge_init'] = 'void setup_wifi() {\n  delay(10);\n  Serial.println();\n  Serial.print("Connecting to ");\n  Serial.println(ssid);\n  WiFi.mode(WIFI_STA);\n  WiFi.begin(ssid, password);\n  while (WiFi.status() != WL_CONNECTED) {\n    delay(500);\n    Serial.print(".");\n  }\n  Serial.println("");\n  Serial.println("WiFi connected");\n  Serial.println("IP address: ");\n  Serial.println(WiFi.localIP());\n}\nString URLEncode(const char* msg)\n{\n  const char *hex = "0123456789abcdef";\n  String encodedMsg = "";\n  while (*msg!=\'\\0\'){\n      if( (\'a\' &lt;= *msg &amp;&amp; *msg &lt;= \'z\')\n              || (\'A\' &lt;= *msg &amp;&amp; *msg &lt;= \'Z\')\n              || (\'0\' &lt;= *msg &amp;&amp; *msg &lt;= \'9\') ) {\n          encodedMsg += *msg;\n      } else {\n          encodedMsg += \'%\';\n          encodedMsg += hex[*msg &gt;&gt; 4];\n          encodedMsg += hex[*msg &amp; 15];\n      }\n      msg++;\n  }\n  return encodedMsg;\n}\nvoid  sendToGoogleSheets(const String&amp; dateInclude,const String&amp; data)\n{\n  sheetTag=URLEncode(sTag);\n  static WiFiClientSecure sheetClient;\n  sheetClient.setInsecure();\n  const char* host="script.google.com";\n  if (sheetClient.connect(host, 443)) {\n      const String url = String() +"https://"+host+"/macros/s/"+asId+"/exec?type=insert&amp;dateInclude="+dateInclude+"&amp;sheetId="+sheetId+"&amp;sheetTag="+sheetTag+"&amp;data="+data;\n      sheetClient.println("GET " + url + " HTTP/1.1");\n      sheetClient.println(String()+"Host: "+host);\n      sheetClient.println("Accept: */*");\n      sheetClient.println("Connection: close");\n      sheetClient.println();\n      sheetClient.println();\n      sheetClient.stop();\n  }\n}\nvoid batCharging(){\n    int interval = 31;//每隔幾秒紀錄一次\n  if(millis()-preMillisBat&gt;=interval*1000){\n      preMillisBat = millis();\n      \n      shuntvoltage = ina219Bat.getShuntVoltage_mV();\n      busvoltage = ina219Bat.getBusVoltage_V();//Bus Voltage電池電壓(V)\n      current_mA = ina219Bat.getCurrent_mA();//Current負載電流(mA)\n      power_mW = ina219Bat.getPower_mW();//Power負載功率(mW)\n      loadvoltage = busvoltage + (shuntvoltage / 1000);//Load Voltage負載電壓(V)\n      \n      //寫入google試算表\n      if(power_mW&gt;0){\n        sendToGoogleSheets("1",URLEncode((String() + "太陽能板產生能量" + "," + power_mW + "," + interval).c_str()));\n      }      \n  }   \n}\nvoid carCharging(){\n    int interval = 61;//每隔幾秒紀錄一次\n  if(millis()-preMillisCar&gt;=interval*1000){\n      preMillisCar = millis();\n      \n      shuntvoltage = ina219Car.getShuntVoltage_mV();\n      busvoltage = ina219Car.getBusVoltage_V();//Bus Voltage電池電壓(V)\n      current_mA = ina219Car.getCurrent_mA(;//Current負載電流(mA)\n      power_mW = ina219Car.getPower_mW();//Power負載功率(mW)\n      loadvoltage = busvoltage + (shuntvoltage / 1000);//Load Voltage負載電壓(V)\n      \n      //寫入google試算表\n      if(power_mW&gt;0){\n        sendToGoogleSheets("1",URLEncode((String() + "小車消耗能量" + "," + power_mW + "," + interval).c_str()));\n      }      \n  }   \n}\n';</v>
+        <v>Blockly.Arduino.functions_['_01imi_espcharge_init'] = 'void setup_wifi() {\n  delay(10);\n  Serial.println();\n  Serial.print("Connecting to ");\n  Serial.println(ssid);\n  WiFi.mode(WIFI_STA);\n  WiFi.begin(ssid, password);\n  while (WiFi.status() != WL_CONNECTED) {\n    delay(500);\n    Serial.print(".");\n  }\n  Serial.println("");\n  Serial.println("WiFi connected");\n  Serial.println("IP address: ");\n  Serial.println(WiFi.localIP());\n}\nString URLEncode(const char* msg)\n{\n  const char *hex = "0123456789abcdef";\n  String encodedMsg = "";\n  while (*msg!=\'\\0\'){\n      if( (\'a\' &lt;= *msg &amp;&amp; *msg &lt;= \'z\')\n              || (\'A\' &lt;= *msg &amp;&amp; *msg &lt;= \'Z\')\n              || (\'0\' &lt;= *msg &amp;&amp; *msg &lt;= \'9\') ) {\n          encodedMsg += *msg;\n      } else {\n          encodedMsg += \'%\';\n          encodedMsg += hex[*msg &gt;&gt; 4];\n          encodedMsg += hex[*msg &amp; 15];\n      }\n      msg++;\n  }\n  return encodedMsg;\n}\nvoid  sendToGoogleSheets(const String&amp; dateInclude,const String&amp; data)\n{\n  sheetTag=URLEncode(sTag);\n  static WiFiClientSecure sheetClient;\n  sheetClient.setInsecure();\n  const char* host="script.google.com";\n  if (sheetClient.connect(host, 443)) {\n      const String url = String() +"https://"+host+"/macros/s/"+asId+"/exec?type=insert&amp;dateInclude="+dateInclude+"&amp;sheetId="+sheetId+"&amp;sheetTag="+sheetTag+"&amp;data="+data;\n      sheetClient.println("GET " + url + " HTTP/1.1");\n      sheetClient.println(String()+"Host: "+host);\n      sheetClient.println("Accept: */*");\n      sheetClient.println("Connection: close");\n      sheetClient.println();\n      sheetClient.println();\n      sheetClient.stop();\n  }\n}\nvoid batCharging(){\n    int interval = 31;//每隔幾秒紀錄一次\n  if(millis()-preMillisBat&gt;=interval*1000){\n      preMillisBat = millis();\n      \n      shuntvoltage = ina219Bat.getShuntVoltage_mV();\n      busvoltage = ina219Bat.getBusVoltage_V();//Bus Voltage電池電壓(V)\n      current_mA = ina219Bat.getCurrent_mA();//Current負載電流(mA)\n      power_mW = ina219Bat.getPower_mW();//Power負載功率(mW)\n      loadvoltage = busvoltage + (shuntvoltage / 1000);//Load Voltage負載電壓(V)\n      \n      //寫入google試算表\n      if(power_mW&gt;0){\n        sendToGoogleSheets("1",URLEncode((String() + "太陽能板產生能量" + "," + power_mW + "," + interval).c_str()));\n      }      \n  }   \n}\nvoid carCharging(){\n    int interval = 61;//每隔幾秒紀錄一次\n  if(millis()-preMillisCar&gt;=interval*1000){\n      preMillisCar = millis();\n      \n      shuntvoltage = ina219Car.getShuntVoltage_mV();\n      busvoltage = ina219Car.getBusVoltage_V();//Bus Voltage電池電壓(V)\n      current_mA = ina219Car.getCurrent_mA();//Current負載電流(mA)\n      power_mW = ina219Car.getPower_mW();//Power負載功率(mW)\n      loadvoltage = busvoltage + (shuntvoltage / 1000);//Load Voltage負載電壓(V)\n      \n      //寫入google試算表\n      if(power_mW&gt;0){\n        sendToGoogleSheets("1",URLEncode((String() + "小車消耗能量" + "," + power_mW + "," + interval).c_str()));\n      }      \n  }   \n}\n';</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -22988,7 +22989,7 @@
       </c>
       <c r="D3" s="5" t="str">
         <f>B2&amp;B3&amp;B4&amp;B5&amp;B6&amp;B7&amp;B8&amp;B9&amp;B10&amp;B11&amp;B12&amp;B13&amp;B14&amp;B15&amp;B16&amp;B17&amp;B18&amp;B19&amp;B20&amp;B21&amp;B22&amp;B23&amp;B24&amp;B25&amp;B26&amp;B27&amp;B28&amp;B29&amp;B30&amp;B31&amp;B32&amp;B33&amp;B34&amp;B35&amp;B36&amp;B37&amp;B38&amp;B39&amp;B40&amp;B41&amp;B42&amp;B43&amp;B44&amp;B45&amp;B46&amp;B47&amp;B48&amp;B49&amp;B50&amp;B51&amp;B52&amp;B53&amp;B54&amp;B55&amp;B56&amp;B57&amp;B58&amp;B59&amp;B60&amp;B61&amp;B62&amp;B63&amp;B64&amp;B65&amp;B66&amp;B67&amp;B68&amp;B69&amp;B70&amp;B71&amp;B72&amp;B73&amp;B74&amp;B75&amp;B76&amp;B77&amp;B78&amp;B79&amp;B80&amp;B81&amp;B82&amp;B83&amp;B84&amp;B85&amp;B86&amp;B87&amp;B88&amp;B89&amp;B90&amp;B91&amp;B92&amp;B93</f>
-        <v>void setup_wifi() {\n  delay(10);\n  Serial.println();\n  Serial.print("Connecting to ");\n  Serial.println(ssid);\n  WiFi.mode(WIFI_STA);\n  WiFi.begin(ssid, password);\n  while (WiFi.status() != WL_CONNECTED) {\n    delay(500);\n    Serial.print(".");\n  }\n  Serial.println("");\n  Serial.println("WiFi connected");\n  Serial.println("IP address: ");\n  Serial.println(WiFi.localIP());\n}\nString URLEncode(const char* msg)\n{\n  const char *hex = "0123456789abcdef";\n  String encodedMsg = "";\n  while (*msg!=\'\\0\'){\n      if( (\'a\' &lt;= *msg &amp;&amp; *msg &lt;= \'z\')\n              || (\'A\' &lt;= *msg &amp;&amp; *msg &lt;= \'Z\')\n              || (\'0\' &lt;= *msg &amp;&amp; *msg &lt;= \'9\') ) {\n          encodedMsg += *msg;\n      } else {\n          encodedMsg += \'%\';\n          encodedMsg += hex[*msg &gt;&gt; 4];\n          encodedMsg += hex[*msg &amp; 15];\n      }\n      msg++;\n  }\n  return encodedMsg;\n}\nvoid  sendToGoogleSheets(const String&amp; dateInclude,const String&amp; data)\n{\n  sheetTag=URLEncode(sTag);\n  static WiFiClientSecure sheetClient;\n  sheetClient.setInsecure();\n  const char* host="script.google.com";\n  if (sheetClient.connect(host, 443)) {\n      const String url = String() +"https://"+host+"/macros/s/"+asId+"/exec?type=insert&amp;dateInclude="+dateInclude+"&amp;sheetId="+sheetId+"&amp;sheetTag="+sheetTag+"&amp;data="+data;\n      sheetClient.println("GET " + url + " HTTP/1.1");\n      sheetClient.println(String()+"Host: "+host);\n      sheetClient.println("Accept: */*");\n      sheetClient.println("Connection: close");\n      sheetClient.println();\n      sheetClient.println();\n      sheetClient.stop();\n  }\n}\nvoid batCharging(){\n    int interval = 31;//每隔幾秒紀錄一次\n  if(millis()-preMillisBat&gt;=interval*1000){\n      preMillisBat = millis();\n      \n      shuntvoltage = ina219Bat.getShuntVoltage_mV();\n      busvoltage = ina219Bat.getBusVoltage_V();//Bus Voltage電池電壓(V)\n      current_mA = ina219Bat.getCurrent_mA();//Current負載電流(mA)\n      power_mW = ina219Bat.getPower_mW();//Power負載功率(mW)\n      loadvoltage = busvoltage + (shuntvoltage / 1000);//Load Voltage負載電壓(V)\n      \n      //寫入google試算表\n      if(power_mW&gt;0){\n        sendToGoogleSheets("1",URLEncode((String() + "太陽能板產生能量" + "," + power_mW + "," + interval).c_str()));\n      }      \n  }   \n}\nvoid carCharging(){\n    int interval = 61;//每隔幾秒紀錄一次\n  if(millis()-preMillisCar&gt;=interval*1000){\n      preMillisCar = millis();\n      \n      shuntvoltage = ina219Car.getShuntVoltage_mV();\n      busvoltage = ina219Car.getBusVoltage_V();//Bus Voltage電池電壓(V)\n      current_mA = ina219Car.getCurrent_mA(;//Current負載電流(mA)\n      power_mW = ina219Car.getPower_mW();//Power負載功率(mW)\n      loadvoltage = busvoltage + (shuntvoltage / 1000);//Load Voltage負載電壓(V)\n      \n      //寫入google試算表\n      if(power_mW&gt;0){\n        sendToGoogleSheets("1",URLEncode((String() + "小車消耗能量" + "," + power_mW + "," + interval).c_str()));\n      }      \n  }   \n}\n</v>
+        <v>void setup_wifi() {\n  delay(10);\n  Serial.println();\n  Serial.print("Connecting to ");\n  Serial.println(ssid);\n  WiFi.mode(WIFI_STA);\n  WiFi.begin(ssid, password);\n  while (WiFi.status() != WL_CONNECTED) {\n    delay(500);\n    Serial.print(".");\n  }\n  Serial.println("");\n  Serial.println("WiFi connected");\n  Serial.println("IP address: ");\n  Serial.println(WiFi.localIP());\n}\nString URLEncode(const char* msg)\n{\n  const char *hex = "0123456789abcdef";\n  String encodedMsg = "";\n  while (*msg!=\'\\0\'){\n      if( (\'a\' &lt;= *msg &amp;&amp; *msg &lt;= \'z\')\n              || (\'A\' &lt;= *msg &amp;&amp; *msg &lt;= \'Z\')\n              || (\'0\' &lt;= *msg &amp;&amp; *msg &lt;= \'9\') ) {\n          encodedMsg += *msg;\n      } else {\n          encodedMsg += \'%\';\n          encodedMsg += hex[*msg &gt;&gt; 4];\n          encodedMsg += hex[*msg &amp; 15];\n      }\n      msg++;\n  }\n  return encodedMsg;\n}\nvoid  sendToGoogleSheets(const String&amp; dateInclude,const String&amp; data)\n{\n  sheetTag=URLEncode(sTag);\n  static WiFiClientSecure sheetClient;\n  sheetClient.setInsecure();\n  const char* host="script.google.com";\n  if (sheetClient.connect(host, 443)) {\n      const String url = String() +"https://"+host+"/macros/s/"+asId+"/exec?type=insert&amp;dateInclude="+dateInclude+"&amp;sheetId="+sheetId+"&amp;sheetTag="+sheetTag+"&amp;data="+data;\n      sheetClient.println("GET " + url + " HTTP/1.1");\n      sheetClient.println(String()+"Host: "+host);\n      sheetClient.println("Accept: */*");\n      sheetClient.println("Connection: close");\n      sheetClient.println();\n      sheetClient.println();\n      sheetClient.stop();\n  }\n}\nvoid batCharging(){\n    int interval = 31;//每隔幾秒紀錄一次\n  if(millis()-preMillisBat&gt;=interval*1000){\n      preMillisBat = millis();\n      \n      shuntvoltage = ina219Bat.getShuntVoltage_mV();\n      busvoltage = ina219Bat.getBusVoltage_V();//Bus Voltage電池電壓(V)\n      current_mA = ina219Bat.getCurrent_mA();//Current負載電流(mA)\n      power_mW = ina219Bat.getPower_mW();//Power負載功率(mW)\n      loadvoltage = busvoltage + (shuntvoltage / 1000);//Load Voltage負載電壓(V)\n      \n      //寫入google試算表\n      if(power_mW&gt;0){\n        sendToGoogleSheets("1",URLEncode((String() + "太陽能板產生能量" + "," + power_mW + "," + interval).c_str()));\n      }      \n  }   \n}\nvoid carCharging(){\n    int interval = 61;//每隔幾秒紀錄一次\n  if(millis()-preMillisCar&gt;=interval*1000){\n      preMillisCar = millis();\n      \n      shuntvoltage = ina219Car.getShuntVoltage_mV();\n      busvoltage = ina219Car.getBusVoltage_V();//Bus Voltage電池電壓(V)\n      current_mA = ina219Car.getCurrent_mA();//Current負載電流(mA)\n      power_mW = ina219Car.getPower_mW();//Power負載功率(mW)\n      loadvoltage = busvoltage + (shuntvoltage / 1000);//Load Voltage負載電壓(V)\n      \n      //寫入google試算表\n      if(power_mW&gt;0){\n        sendToGoogleSheets("1",URLEncode((String() + "小車消耗能量" + "," + power_mW + "," + interval).c_str()));\n      }      \n  }   \n}\n</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -23699,16 +23700,16 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="37" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="B84" s="18" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">      current_mA = ina219Car.getCurrent_mA(;//Current負載電流(mA)\n</v>
+        <v xml:space="preserve">      current_mA = ina219Car.getCurrent_mA();//Current負載電流(mA)\n</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="37" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B85" s="18" t="str">
         <f t="shared" si="1"/>
@@ -23753,7 +23754,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="37" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B90" s="18" t="str">
         <f t="shared" si="1"/>
